--- a/SuppXLS/Scen_Base_VS.xlsx
+++ b/SuppXLS/Scen_Base_VS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_grids\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61722B11-B489-49B8-82F6-8A2071676025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5298C102-163B-45CD-A8CF-086018D2331F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="5" r:id="rId1"/>
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3630" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3630" uniqueCount="727">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -2305,6 +2305,9 @@
   </si>
   <si>
     <t>attrib_cond</t>
+  </si>
+  <si>
+    <t>deact tfm_ins-at</t>
   </si>
 </sst>
 </file>
@@ -2861,7 +2864,7 @@
         <v>299</v>
       </c>
       <c r="AA3" t="s">
-        <v>252</v>
+        <v>726</v>
       </c>
     </row>
     <row r="4" spans="2:42" x14ac:dyDescent="0.45">

--- a/SuppXLS/Scen_Base_VS.xlsx
+++ b/SuppXLS/Scen_Base_VS.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5298C102-163B-45CD-A8CF-086018D2331F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED54EE4-F3B5-4902-B9AD-5CDD96F5236F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="5" r:id="rId1"/>
-    <sheet name="Veda" sheetId="1" r:id="rId2"/>
-    <sheet name="buildrates" sheetId="4" r:id="rId3"/>
-    <sheet name="historical_data_long" sheetId="3" r:id="rId4"/>
+    <sheet name="VS-EECA links" sheetId="6" r:id="rId2"/>
+    <sheet name="Veda" sheetId="1" r:id="rId3"/>
+    <sheet name="buildrates" sheetId="4" r:id="rId4"/>
+    <sheet name="historical_data_long" sheetId="3" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">grids!$AM$9:$AO$163</definedName>
@@ -127,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3630" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3900" uniqueCount="759">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -2308,6 +2309,102 @@
   </si>
   <si>
     <t>deact tfm_ins-at</t>
+  </si>
+  <si>
+    <t>bus_id</t>
+  </si>
+  <si>
+    <t>island</t>
+  </si>
+  <si>
+    <t>NI</t>
+  </si>
+  <si>
+    <t>NZ11-220</t>
+  </si>
+  <si>
+    <t>NZ13-220</t>
+  </si>
+  <si>
+    <t>NZ27-220</t>
+  </si>
+  <si>
+    <t>w87928925-220</t>
+  </si>
+  <si>
+    <t>w94053861-220</t>
+  </si>
+  <si>
+    <t>w95344674-220</t>
+  </si>
+  <si>
+    <t>w119877500-220</t>
+  </si>
+  <si>
+    <t>w167285260-220</t>
+  </si>
+  <si>
+    <t>w167285336-220</t>
+  </si>
+  <si>
+    <t>w167300914-220</t>
+  </si>
+  <si>
+    <t>w270022030-220</t>
+  </si>
+  <si>
+    <t>w907631032-220</t>
+  </si>
+  <si>
+    <t>w1167708390-220</t>
+  </si>
+  <si>
+    <t>w1363994055-220</t>
+  </si>
+  <si>
+    <t>w33795353-220</t>
+  </si>
+  <si>
+    <t>w270521928-220</t>
+  </si>
+  <si>
+    <t>w95343089-220</t>
+  </si>
+  <si>
+    <t>w100957314-220</t>
+  </si>
+  <si>
+    <t>w167286837-220</t>
+  </si>
+  <si>
+    <t>w180519027-220</t>
+  </si>
+  <si>
+    <t>w268826084-220</t>
+  </si>
+  <si>
+    <t>w272195826-220</t>
+  </si>
+  <si>
+    <t>RESELC</t>
+  </si>
+  <si>
+    <t>COMELC</t>
+  </si>
+  <si>
+    <t>TRAELC</t>
+  </si>
+  <si>
+    <t>INDELC</t>
+  </si>
+  <si>
+    <t>AGRELC</t>
+  </si>
+  <si>
+    <t>RESELC,COMELC,TRAELC</t>
+  </si>
+  <si>
+    <t>~TFM_INS-TS: attribute=FLO_SHAR</t>
   </si>
 </sst>
 </file>
@@ -12536,6 +12633,2433 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76B3EC81-2889-429D-9E2D-D5BB4326DD32}">
+  <dimension ref="B2:V54"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.46484375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.86328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.9296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.46484375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.86328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="11.86328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="L2" t="s">
+        <v>727</v>
+      </c>
+      <c r="M2" t="s">
+        <v>728</v>
+      </c>
+      <c r="N2" t="s">
+        <v>752</v>
+      </c>
+      <c r="O2" t="s">
+        <v>753</v>
+      </c>
+      <c r="P2" t="s">
+        <v>754</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>755</v>
+      </c>
+      <c r="R2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="3" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B3" t="s">
+        <v>722</v>
+      </c>
+      <c r="L3" t="s">
+        <v>733</v>
+      </c>
+      <c r="M3" t="s">
+        <v>729</v>
+      </c>
+      <c r="N3" s="2">
+        <v>5.86636006449012E-3</v>
+      </c>
+      <c r="O3" s="2">
+        <v>5.8663600644901E-3</v>
+      </c>
+      <c r="P3" s="2">
+        <v>5.8663600644900896E-3</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>2.0049350726642299E-2</v>
+      </c>
+      <c r="R3" s="2">
+        <v>7.0394854969028198E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C4" t="s">
+        <v>253</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" t="s">
+        <v>299</v>
+      </c>
+      <c r="L4" t="s">
+        <v>734</v>
+      </c>
+      <c r="M4" t="s">
+        <v>729</v>
+      </c>
+      <c r="N4" s="2">
+        <v>8.1561509900455104E-2</v>
+      </c>
+      <c r="O4" s="2">
+        <v>8.1561509900455104E-2</v>
+      </c>
+      <c r="P4" s="2">
+        <v>8.1561509900455104E-2</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>8.06356741102075E-2</v>
+      </c>
+      <c r="R4" s="2">
+        <v>6.8580675281546405E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B5" t="str">
+        <f>M3</f>
+        <v>NI</v>
+      </c>
+      <c r="C5" t="str">
+        <f>"e_"&amp;L3</f>
+        <v>e_w87928925-220</v>
+      </c>
+      <c r="D5" t="s">
+        <v>724</v>
+      </c>
+      <c r="E5" t="s">
+        <v>723</v>
+      </c>
+      <c r="F5" t="s">
+        <v>301</v>
+      </c>
+      <c r="L5" t="s">
+        <v>735</v>
+      </c>
+      <c r="M5" t="s">
+        <v>729</v>
+      </c>
+      <c r="N5" s="2">
+        <v>1.7030252471331601E-2</v>
+      </c>
+      <c r="O5" s="2">
+        <v>1.7030252471331601E-2</v>
+      </c>
+      <c r="P5" s="2">
+        <v>1.7030252471331601E-2</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>2.8984919214794801E-2</v>
+      </c>
+      <c r="R5" s="2">
+        <v>0.12292330838603201</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B6" t="str">
+        <f t="shared" ref="B6:B26" si="0">M4</f>
+        <v>NI</v>
+      </c>
+      <c r="C6" t="str">
+        <f t="shared" ref="C6:C26" si="1">"e_"&amp;L4</f>
+        <v>e_w94053861-220</v>
+      </c>
+      <c r="D6" t="s">
+        <v>724</v>
+      </c>
+      <c r="E6" t="s">
+        <v>723</v>
+      </c>
+      <c r="F6" t="s">
+        <v>301</v>
+      </c>
+      <c r="L6" t="s">
+        <v>736</v>
+      </c>
+      <c r="M6" t="s">
+        <v>729</v>
+      </c>
+      <c r="N6" s="2">
+        <v>6.5397898449555403E-2</v>
+      </c>
+      <c r="O6" s="2">
+        <v>6.5397898449555403E-2</v>
+      </c>
+      <c r="P6" s="2">
+        <v>6.5397898449555403E-2</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>6.7698335422951006E-2</v>
+      </c>
+      <c r="R6" s="2">
+        <v>3.9503551970168603E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B7" t="str">
+        <f t="shared" si="0"/>
+        <v>NI</v>
+      </c>
+      <c r="C7" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w95344674-220</v>
+      </c>
+      <c r="D7" t="s">
+        <v>724</v>
+      </c>
+      <c r="E7" t="s">
+        <v>723</v>
+      </c>
+      <c r="F7" t="s">
+        <v>301</v>
+      </c>
+      <c r="L7" t="s">
+        <v>737</v>
+      </c>
+      <c r="M7" t="s">
+        <v>729</v>
+      </c>
+      <c r="N7" s="2">
+        <v>1.0210371164411E-2</v>
+      </c>
+      <c r="O7" s="2">
+        <v>1.0210371164411E-2</v>
+      </c>
+      <c r="P7" s="2">
+        <v>1.0210371164410899E-2</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>2.3526292933004799E-2</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0.11850700547946599</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B8" t="str">
+        <f t="shared" si="0"/>
+        <v>NI</v>
+      </c>
+      <c r="C8" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w119877500-220</v>
+      </c>
+      <c r="D8" t="s">
+        <v>724</v>
+      </c>
+      <c r="E8" t="s">
+        <v>723</v>
+      </c>
+      <c r="F8" t="s">
+        <v>301</v>
+      </c>
+      <c r="L8" t="s">
+        <v>738</v>
+      </c>
+      <c r="M8" t="s">
+        <v>729</v>
+      </c>
+      <c r="N8" s="2">
+        <v>7.6938704058300096E-3</v>
+      </c>
+      <c r="O8" s="2">
+        <v>7.69387040583E-3</v>
+      </c>
+      <c r="P8" s="2">
+        <v>7.69387040583E-3</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>2.1512088204104898E-2</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0.11113019841467001</v>
+      </c>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B9" t="str">
+        <f t="shared" si="0"/>
+        <v>NI</v>
+      </c>
+      <c r="C9" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w167285260-220</v>
+      </c>
+      <c r="D9" t="s">
+        <v>724</v>
+      </c>
+      <c r="E9" t="s">
+        <v>723</v>
+      </c>
+      <c r="F9" t="s">
+        <v>301</v>
+      </c>
+      <c r="L9" t="s">
+        <v>739</v>
+      </c>
+      <c r="M9" t="s">
+        <v>729</v>
+      </c>
+      <c r="N9" s="2">
+        <v>3.2952241812295398E-2</v>
+      </c>
+      <c r="O9" s="2">
+        <v>3.2952241812295398E-2</v>
+      </c>
+      <c r="P9" s="2">
+        <v>3.2952241812295398E-2</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>4.1728863803209698E-2</v>
+      </c>
+      <c r="R9" s="2">
+        <v>0.125235778416185</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B10" t="str">
+        <f t="shared" si="0"/>
+        <v>NI</v>
+      </c>
+      <c r="C10" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w167285336-220</v>
+      </c>
+      <c r="D10" t="s">
+        <v>724</v>
+      </c>
+      <c r="E10" t="s">
+        <v>723</v>
+      </c>
+      <c r="F10" t="s">
+        <v>301</v>
+      </c>
+      <c r="L10" t="s">
+        <v>740</v>
+      </c>
+      <c r="M10" t="s">
+        <v>729</v>
+      </c>
+      <c r="N10" s="2">
+        <v>2.34291321054837E-2</v>
+      </c>
+      <c r="O10" s="2">
+        <v>2.3429132105483801E-2</v>
+      </c>
+      <c r="P10" s="2">
+        <v>2.3429132105483801E-2</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>3.4106576172306398E-2</v>
+      </c>
+      <c r="R10" s="2">
+        <v>9.4538907932051705E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B11" t="str">
+        <f t="shared" si="0"/>
+        <v>NI</v>
+      </c>
+      <c r="C11" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w167300914-220</v>
+      </c>
+      <c r="D11" t="s">
+        <v>724</v>
+      </c>
+      <c r="E11" t="s">
+        <v>723</v>
+      </c>
+      <c r="F11" t="s">
+        <v>301</v>
+      </c>
+      <c r="L11" t="s">
+        <v>741</v>
+      </c>
+      <c r="M11" t="s">
+        <v>729</v>
+      </c>
+      <c r="N11" s="2">
+        <v>0.63543589233768305</v>
+      </c>
+      <c r="O11" s="2">
+        <v>0.63543589233768305</v>
+      </c>
+      <c r="P11" s="2">
+        <v>0.63543589233768305</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>0.52395618435339197</v>
+      </c>
+      <c r="R11" s="2">
+        <v>4.2286542778396897E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B12" t="str">
+        <f t="shared" si="0"/>
+        <v>NI</v>
+      </c>
+      <c r="C12" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w270022030-220</v>
+      </c>
+      <c r="D12" t="s">
+        <v>724</v>
+      </c>
+      <c r="E12" t="s">
+        <v>723</v>
+      </c>
+      <c r="F12" t="s">
+        <v>301</v>
+      </c>
+      <c r="L12" t="s">
+        <v>742</v>
+      </c>
+      <c r="M12" t="s">
+        <v>729</v>
+      </c>
+      <c r="N12" s="2">
+        <v>8.5661305450976596E-3</v>
+      </c>
+      <c r="O12" s="2">
+        <v>8.5661305450976995E-3</v>
+      </c>
+      <c r="P12" s="2">
+        <v>8.5661305450976891E-3</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>2.2210244360566699E-2</v>
+      </c>
+      <c r="R12" s="2">
+        <v>9.8552632363159004E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B13" t="str">
+        <f t="shared" si="0"/>
+        <v>NI</v>
+      </c>
+      <c r="C13" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w907631032-220</v>
+      </c>
+      <c r="D13" t="s">
+        <v>724</v>
+      </c>
+      <c r="E13" t="s">
+        <v>723</v>
+      </c>
+      <c r="F13" t="s">
+        <v>301</v>
+      </c>
+      <c r="L13" t="s">
+        <v>743</v>
+      </c>
+      <c r="M13" t="s">
+        <v>729</v>
+      </c>
+      <c r="N13" s="2">
+        <v>8.8870686785993705E-2</v>
+      </c>
+      <c r="O13" s="2">
+        <v>8.8870686785993594E-2</v>
+      </c>
+      <c r="P13" s="2">
+        <v>8.8870686785993594E-2</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>8.6485932091261195E-2</v>
+      </c>
+      <c r="R13" s="2">
+        <v>4.8221286775162204E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B14" t="str">
+        <f t="shared" si="0"/>
+        <v>NI</v>
+      </c>
+      <c r="C14" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w1167708390-220</v>
+      </c>
+      <c r="D14" t="s">
+        <v>724</v>
+      </c>
+      <c r="E14" t="s">
+        <v>723</v>
+      </c>
+      <c r="F14" t="s">
+        <v>301</v>
+      </c>
+      <c r="L14" t="s">
+        <v>730</v>
+      </c>
+      <c r="M14" t="s">
+        <v>729</v>
+      </c>
+      <c r="N14" s="2">
+        <v>8.0617065696143696E-3</v>
+      </c>
+      <c r="O14" s="2">
+        <v>8.0617065696143003E-3</v>
+      </c>
+      <c r="P14" s="2">
+        <v>8.0617065696143003E-3</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>2.18065039073502E-2</v>
+      </c>
+      <c r="R14" s="2">
+        <v>8.1145533401035905E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B15" t="str">
+        <f t="shared" si="0"/>
+        <v>NI</v>
+      </c>
+      <c r="C15" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w1363994055-220</v>
+      </c>
+      <c r="D15" t="s">
+        <v>724</v>
+      </c>
+      <c r="E15" t="s">
+        <v>723</v>
+      </c>
+      <c r="F15" t="s">
+        <v>301</v>
+      </c>
+      <c r="L15" t="s">
+        <v>731</v>
+      </c>
+      <c r="M15" t="s">
+        <v>729</v>
+      </c>
+      <c r="N15" s="2">
+        <v>1.4923947387757999E-2</v>
+      </c>
+      <c r="O15" s="2">
+        <v>1.49239473877581E-2</v>
+      </c>
+      <c r="P15" s="2">
+        <v>1.49239473877581E-2</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>2.7299034700207302E-2</v>
+      </c>
+      <c r="R15" s="2">
+        <v>6.04367704312977E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B16" t="str">
+        <f t="shared" si="0"/>
+        <v>NI</v>
+      </c>
+      <c r="C16" t="str">
+        <f t="shared" si="1"/>
+        <v>e_NZ11-220</v>
+      </c>
+      <c r="D16" t="s">
+        <v>724</v>
+      </c>
+      <c r="E16" t="s">
+        <v>723</v>
+      </c>
+      <c r="F16" t="s">
+        <v>301</v>
+      </c>
+      <c r="L16" t="s">
+        <v>744</v>
+      </c>
+      <c r="M16" t="s">
+        <v>721</v>
+      </c>
+      <c r="N16" s="2">
+        <v>2.1443297887408799E-2</v>
+      </c>
+      <c r="O16" s="2">
+        <v>2.1696550845568201E-2</v>
+      </c>
+      <c r="P16" s="2">
+        <v>2.1696550845568201E-2</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>4.2007495042417201E-2</v>
+      </c>
+      <c r="R16" s="2">
+        <v>6.3638923649862705E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B17" t="str">
+        <f t="shared" si="0"/>
+        <v>NI</v>
+      </c>
+      <c r="C17" t="str">
+        <f t="shared" si="1"/>
+        <v>e_NZ13-220</v>
+      </c>
+      <c r="D17" t="s">
+        <v>724</v>
+      </c>
+      <c r="E17" t="s">
+        <v>723</v>
+      </c>
+      <c r="F17" t="s">
+        <v>301</v>
+      </c>
+      <c r="L17" t="s">
+        <v>745</v>
+      </c>
+      <c r="M17" t="s">
+        <v>721</v>
+      </c>
+      <c r="N17" s="2">
+        <v>1.7574323650842699E-2</v>
+      </c>
+      <c r="O17" s="2">
+        <v>1.7781882650190501E-2</v>
+      </c>
+      <c r="P17" s="2">
+        <v>1.77818826501904E-2</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>3.9025821902286997E-2</v>
+      </c>
+      <c r="R17" s="2">
+        <v>0.142535486755099</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B18" t="str">
+        <f t="shared" si="0"/>
+        <v>SI</v>
+      </c>
+      <c r="C18" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w33795353-220</v>
+      </c>
+      <c r="D18" t="s">
+        <v>724</v>
+      </c>
+      <c r="E18" t="s">
+        <v>723</v>
+      </c>
+      <c r="F18" t="s">
+        <v>301</v>
+      </c>
+      <c r="L18" t="s">
+        <v>746</v>
+      </c>
+      <c r="M18" t="s">
+        <v>721</v>
+      </c>
+      <c r="N18" s="2">
+        <v>0.28354990845613498</v>
+      </c>
+      <c r="O18" s="2">
+        <v>0.28689873350531298</v>
+      </c>
+      <c r="P18" s="2">
+        <v>0.28689873350531298</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>0.244003216078024</v>
+      </c>
+      <c r="R18" s="2">
+        <v>3.1587285738253097E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B19" t="str">
+        <f t="shared" si="0"/>
+        <v>SI</v>
+      </c>
+      <c r="C19" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w270521928-220</v>
+      </c>
+      <c r="D19" t="s">
+        <v>724</v>
+      </c>
+      <c r="E19" t="s">
+        <v>723</v>
+      </c>
+      <c r="F19" t="s">
+        <v>301</v>
+      </c>
+      <c r="L19" t="s">
+        <v>747</v>
+      </c>
+      <c r="M19" t="s">
+        <v>721</v>
+      </c>
+      <c r="N19" s="2">
+        <v>0.50257319574648895</v>
+      </c>
+      <c r="O19" s="2">
+        <v>0.50850876354873298</v>
+      </c>
+      <c r="P19" s="2">
+        <v>0.50850876354873298</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>0.41279623790913</v>
+      </c>
+      <c r="R19" s="2">
+        <v>3.2834920354623598E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B20" t="str">
+        <f t="shared" si="0"/>
+        <v>SI</v>
+      </c>
+      <c r="C20" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w95343089-220</v>
+      </c>
+      <c r="D20" t="s">
+        <v>724</v>
+      </c>
+      <c r="E20" t="s">
+        <v>723</v>
+      </c>
+      <c r="F20" t="s">
+        <v>301</v>
+      </c>
+      <c r="L20" t="s">
+        <v>748</v>
+      </c>
+      <c r="M20" t="s">
+        <v>721</v>
+      </c>
+      <c r="N20" s="2">
+        <v>3.60680205016288E-2</v>
+      </c>
+      <c r="O20" s="2">
+        <v>3.6493996624096303E-2</v>
+      </c>
+      <c r="P20" s="2">
+        <v>3.6493996624096199E-2</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>5.3278219512109801E-2</v>
+      </c>
+      <c r="R20" s="2">
+        <v>0.191013906423359</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B21" t="str">
+        <f t="shared" si="0"/>
+        <v>SI</v>
+      </c>
+      <c r="C21" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w100957314-220</v>
+      </c>
+      <c r="D21" t="s">
+        <v>724</v>
+      </c>
+      <c r="E21" t="s">
+        <v>723</v>
+      </c>
+      <c r="F21" t="s">
+        <v>301</v>
+      </c>
+      <c r="L21" t="s">
+        <v>749</v>
+      </c>
+      <c r="M21" t="s">
+        <v>721</v>
+      </c>
+      <c r="N21" s="2">
+        <v>3.34436756042156E-2</v>
+      </c>
+      <c r="O21" s="2">
+        <v>2.2028302387549499E-2</v>
+      </c>
+      <c r="P21" s="2">
+        <v>2.2028302387549398E-2</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>5.1255735460109399E-2</v>
+      </c>
+      <c r="R21" s="2">
+        <v>4.7306892983382899E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B22" t="str">
+        <f t="shared" si="0"/>
+        <v>SI</v>
+      </c>
+      <c r="C22" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w167286837-220</v>
+      </c>
+      <c r="D22" t="s">
+        <v>724</v>
+      </c>
+      <c r="E22" t="s">
+        <v>723</v>
+      </c>
+      <c r="F22" t="s">
+        <v>301</v>
+      </c>
+      <c r="L22" t="s">
+        <v>750</v>
+      </c>
+      <c r="M22" t="s">
+        <v>721</v>
+      </c>
+      <c r="N22" s="2">
+        <v>2.3213845419396702E-2</v>
+      </c>
+      <c r="O22" s="2">
+        <v>2.34880091722665E-2</v>
+      </c>
+      <c r="P22" s="2">
+        <v>2.3488009172266601E-2</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>4.3371989530273498E-2</v>
+      </c>
+      <c r="R22" s="2">
+        <v>0.12562350163285799</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B23" t="str">
+        <f t="shared" si="0"/>
+        <v>SI</v>
+      </c>
+      <c r="C23" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w180519027-220</v>
+      </c>
+      <c r="D23" t="s">
+        <v>724</v>
+      </c>
+      <c r="E23" t="s">
+        <v>723</v>
+      </c>
+      <c r="F23" t="s">
+        <v>301</v>
+      </c>
+      <c r="L23" t="s">
+        <v>751</v>
+      </c>
+      <c r="M23" t="s">
+        <v>721</v>
+      </c>
+      <c r="N23" s="2">
+        <v>6.2460982378461698E-2</v>
+      </c>
+      <c r="O23" s="2">
+        <v>6.3198668747412298E-2</v>
+      </c>
+      <c r="P23" s="2">
+        <v>6.3198668747412298E-2</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>7.3618284011086901E-2</v>
+      </c>
+      <c r="R23" s="2">
+        <v>0.16693725652546401</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B24" t="str">
+        <f t="shared" si="0"/>
+        <v>SI</v>
+      </c>
+      <c r="C24" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w268826084-220</v>
+      </c>
+      <c r="D24" t="s">
+        <v>724</v>
+      </c>
+      <c r="E24" t="s">
+        <v>723</v>
+      </c>
+      <c r="F24" t="s">
+        <v>301</v>
+      </c>
+      <c r="L24" t="s">
+        <v>732</v>
+      </c>
+      <c r="M24" t="s">
+        <v>721</v>
+      </c>
+      <c r="N24" s="2">
+        <v>1.9672750355421001E-2</v>
+      </c>
+      <c r="O24" s="2">
+        <v>1.9905092518869998E-2</v>
+      </c>
+      <c r="P24" s="2">
+        <v>1.9905092518869901E-2</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>4.0643000554560903E-2</v>
+      </c>
+      <c r="R24" s="2">
+        <v>0.198521825937094</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B25" t="str">
+        <f t="shared" si="0"/>
+        <v>SI</v>
+      </c>
+      <c r="C25" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w272195826-220</v>
+      </c>
+      <c r="D25" t="s">
+        <v>724</v>
+      </c>
+      <c r="E25" t="s">
+        <v>723</v>
+      </c>
+      <c r="F25" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B26" t="str">
+        <f t="shared" si="0"/>
+        <v>SI</v>
+      </c>
+      <c r="C26" t="str">
+        <f t="shared" si="1"/>
+        <v>e_NZ27-220</v>
+      </c>
+      <c r="D26" t="s">
+        <v>724</v>
+      </c>
+      <c r="E26" t="s">
+        <v>723</v>
+      </c>
+      <c r="F26" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B31" t="s">
+        <v>758</v>
+      </c>
+      <c r="J31" t="s">
+        <v>758</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B32" t="s">
+        <v>311</v>
+      </c>
+      <c r="C32" t="s">
+        <v>253</v>
+      </c>
+      <c r="D32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F32">
+        <v>2020</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="J32" t="s">
+        <v>311</v>
+      </c>
+      <c r="K32" t="s">
+        <v>253</v>
+      </c>
+      <c r="L32" t="s">
+        <v>14</v>
+      </c>
+      <c r="M32" t="s">
+        <v>38</v>
+      </c>
+      <c r="N32">
+        <v>2020</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>311</v>
+      </c>
+      <c r="R32" t="s">
+        <v>253</v>
+      </c>
+      <c r="S32" t="s">
+        <v>14</v>
+      </c>
+      <c r="T32" t="s">
+        <v>38</v>
+      </c>
+      <c r="U32">
+        <v>2020</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B33" t="str">
+        <f>B5</f>
+        <v>NI</v>
+      </c>
+      <c r="C33" t="str">
+        <f>C5</f>
+        <v>e_w87928925-220</v>
+      </c>
+      <c r="D33" t="s">
+        <v>757</v>
+      </c>
+      <c r="E33" t="s">
+        <v>723</v>
+      </c>
+      <c r="F33" s="2"/>
+      <c r="G33">
+        <v>3</v>
+      </c>
+      <c r="J33" t="str">
+        <f>$B33</f>
+        <v>NI</v>
+      </c>
+      <c r="K33" t="str">
+        <f>$C33</f>
+        <v>e_w87928925-220</v>
+      </c>
+      <c r="L33" t="s">
+        <v>756</v>
+      </c>
+      <c r="M33" t="s">
+        <v>723</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33">
+        <v>3</v>
+      </c>
+      <c r="Q33" t="str">
+        <f>$B33</f>
+        <v>NI</v>
+      </c>
+      <c r="R33" t="str">
+        <f>$C33</f>
+        <v>e_w87928925-220</v>
+      </c>
+      <c r="S33" t="s">
+        <v>755</v>
+      </c>
+      <c r="T33" t="s">
+        <v>723</v>
+      </c>
+      <c r="U33" s="2"/>
+      <c r="V33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B34" t="str">
+        <f t="shared" ref="B34:C54" si="2">B6</f>
+        <v>NI</v>
+      </c>
+      <c r="C34" t="str">
+        <f t="shared" si="2"/>
+        <v>e_w94053861-220</v>
+      </c>
+      <c r="D34" t="s">
+        <v>757</v>
+      </c>
+      <c r="E34" t="s">
+        <v>723</v>
+      </c>
+      <c r="F34" s="2">
+        <f t="shared" ref="F34:F54" si="3">N4</f>
+        <v>8.1561509900455104E-2</v>
+      </c>
+      <c r="G34">
+        <v>3</v>
+      </c>
+      <c r="J34" t="str">
+        <f t="shared" ref="J34:J54" si="4">$B34</f>
+        <v>NI</v>
+      </c>
+      <c r="K34" t="str">
+        <f t="shared" ref="K34:K54" si="5">$C34</f>
+        <v>e_w94053861-220</v>
+      </c>
+      <c r="L34" t="s">
+        <v>756</v>
+      </c>
+      <c r="M34" t="s">
+        <v>723</v>
+      </c>
+      <c r="N34" s="2">
+        <f t="shared" ref="N34:N45" si="6">R4</f>
+        <v>6.8580675281546405E-2</v>
+      </c>
+      <c r="O34">
+        <v>3</v>
+      </c>
+      <c r="Q34" t="str">
+        <f t="shared" ref="Q34:Q54" si="7">$B34</f>
+        <v>NI</v>
+      </c>
+      <c r="R34" t="str">
+        <f t="shared" ref="R34:R54" si="8">$C34</f>
+        <v>e_w94053861-220</v>
+      </c>
+      <c r="S34" t="s">
+        <v>755</v>
+      </c>
+      <c r="T34" t="s">
+        <v>723</v>
+      </c>
+      <c r="U34" s="2">
+        <f t="shared" ref="U34:U54" si="9">Q4</f>
+        <v>8.06356741102075E-2</v>
+      </c>
+      <c r="V34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B35" t="str">
+        <f t="shared" si="2"/>
+        <v>NI</v>
+      </c>
+      <c r="C35" t="str">
+        <f t="shared" si="2"/>
+        <v>e_w95344674-220</v>
+      </c>
+      <c r="D35" t="s">
+        <v>757</v>
+      </c>
+      <c r="E35" t="s">
+        <v>723</v>
+      </c>
+      <c r="F35" s="2">
+        <f t="shared" si="3"/>
+        <v>1.7030252471331601E-2</v>
+      </c>
+      <c r="G35">
+        <v>3</v>
+      </c>
+      <c r="J35" t="str">
+        <f t="shared" si="4"/>
+        <v>NI</v>
+      </c>
+      <c r="K35" t="str">
+        <f t="shared" si="5"/>
+        <v>e_w95344674-220</v>
+      </c>
+      <c r="L35" t="s">
+        <v>756</v>
+      </c>
+      <c r="M35" t="s">
+        <v>723</v>
+      </c>
+      <c r="N35" s="2">
+        <f t="shared" si="6"/>
+        <v>0.12292330838603201</v>
+      </c>
+      <c r="O35">
+        <v>3</v>
+      </c>
+      <c r="Q35" t="str">
+        <f t="shared" si="7"/>
+        <v>NI</v>
+      </c>
+      <c r="R35" t="str">
+        <f t="shared" si="8"/>
+        <v>e_w95344674-220</v>
+      </c>
+      <c r="S35" t="s">
+        <v>755</v>
+      </c>
+      <c r="T35" t="s">
+        <v>723</v>
+      </c>
+      <c r="U35" s="2">
+        <f t="shared" si="9"/>
+        <v>2.8984919214794801E-2</v>
+      </c>
+      <c r="V35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B36" t="str">
+        <f t="shared" si="2"/>
+        <v>NI</v>
+      </c>
+      <c r="C36" t="str">
+        <f t="shared" si="2"/>
+        <v>e_w119877500-220</v>
+      </c>
+      <c r="D36" t="s">
+        <v>757</v>
+      </c>
+      <c r="E36" t="s">
+        <v>723</v>
+      </c>
+      <c r="F36" s="2">
+        <f t="shared" si="3"/>
+        <v>6.5397898449555403E-2</v>
+      </c>
+      <c r="G36">
+        <v>3</v>
+      </c>
+      <c r="J36" t="str">
+        <f t="shared" si="4"/>
+        <v>NI</v>
+      </c>
+      <c r="K36" t="str">
+        <f t="shared" si="5"/>
+        <v>e_w119877500-220</v>
+      </c>
+      <c r="L36" t="s">
+        <v>756</v>
+      </c>
+      <c r="M36" t="s">
+        <v>723</v>
+      </c>
+      <c r="N36" s="2">
+        <f t="shared" si="6"/>
+        <v>3.9503551970168603E-2</v>
+      </c>
+      <c r="O36">
+        <v>3</v>
+      </c>
+      <c r="Q36" t="str">
+        <f t="shared" si="7"/>
+        <v>NI</v>
+      </c>
+      <c r="R36" t="str">
+        <f t="shared" si="8"/>
+        <v>e_w119877500-220</v>
+      </c>
+      <c r="S36" t="s">
+        <v>755</v>
+      </c>
+      <c r="T36" t="s">
+        <v>723</v>
+      </c>
+      <c r="U36" s="2">
+        <f t="shared" si="9"/>
+        <v>6.7698335422951006E-2</v>
+      </c>
+      <c r="V36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B37" t="str">
+        <f t="shared" si="2"/>
+        <v>NI</v>
+      </c>
+      <c r="C37" t="str">
+        <f t="shared" si="2"/>
+        <v>e_w167285260-220</v>
+      </c>
+      <c r="D37" t="s">
+        <v>757</v>
+      </c>
+      <c r="E37" t="s">
+        <v>723</v>
+      </c>
+      <c r="F37" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0210371164411E-2</v>
+      </c>
+      <c r="G37">
+        <v>3</v>
+      </c>
+      <c r="J37" t="str">
+        <f t="shared" si="4"/>
+        <v>NI</v>
+      </c>
+      <c r="K37" t="str">
+        <f t="shared" si="5"/>
+        <v>e_w167285260-220</v>
+      </c>
+      <c r="L37" t="s">
+        <v>756</v>
+      </c>
+      <c r="M37" t="s">
+        <v>723</v>
+      </c>
+      <c r="N37" s="2">
+        <f t="shared" si="6"/>
+        <v>0.11850700547946599</v>
+      </c>
+      <c r="O37">
+        <v>3</v>
+      </c>
+      <c r="Q37" t="str">
+        <f t="shared" si="7"/>
+        <v>NI</v>
+      </c>
+      <c r="R37" t="str">
+        <f t="shared" si="8"/>
+        <v>e_w167285260-220</v>
+      </c>
+      <c r="S37" t="s">
+        <v>755</v>
+      </c>
+      <c r="T37" t="s">
+        <v>723</v>
+      </c>
+      <c r="U37" s="2">
+        <f t="shared" si="9"/>
+        <v>2.3526292933004799E-2</v>
+      </c>
+      <c r="V37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B38" t="str">
+        <f t="shared" si="2"/>
+        <v>NI</v>
+      </c>
+      <c r="C38" t="str">
+        <f t="shared" si="2"/>
+        <v>e_w167285336-220</v>
+      </c>
+      <c r="D38" t="s">
+        <v>757</v>
+      </c>
+      <c r="E38" t="s">
+        <v>723</v>
+      </c>
+      <c r="F38" s="2">
+        <f t="shared" si="3"/>
+        <v>7.6938704058300096E-3</v>
+      </c>
+      <c r="G38">
+        <v>3</v>
+      </c>
+      <c r="J38" t="str">
+        <f t="shared" si="4"/>
+        <v>NI</v>
+      </c>
+      <c r="K38" t="str">
+        <f t="shared" si="5"/>
+        <v>e_w167285336-220</v>
+      </c>
+      <c r="L38" t="s">
+        <v>756</v>
+      </c>
+      <c r="M38" t="s">
+        <v>723</v>
+      </c>
+      <c r="N38" s="2">
+        <f t="shared" si="6"/>
+        <v>0.11113019841467001</v>
+      </c>
+      <c r="O38">
+        <v>3</v>
+      </c>
+      <c r="Q38" t="str">
+        <f t="shared" si="7"/>
+        <v>NI</v>
+      </c>
+      <c r="R38" t="str">
+        <f t="shared" si="8"/>
+        <v>e_w167285336-220</v>
+      </c>
+      <c r="S38" t="s">
+        <v>755</v>
+      </c>
+      <c r="T38" t="s">
+        <v>723</v>
+      </c>
+      <c r="U38" s="2">
+        <f t="shared" si="9"/>
+        <v>2.1512088204104898E-2</v>
+      </c>
+      <c r="V38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B39" t="str">
+        <f t="shared" si="2"/>
+        <v>NI</v>
+      </c>
+      <c r="C39" t="str">
+        <f t="shared" si="2"/>
+        <v>e_w167300914-220</v>
+      </c>
+      <c r="D39" t="s">
+        <v>757</v>
+      </c>
+      <c r="E39" t="s">
+        <v>723</v>
+      </c>
+      <c r="F39" s="2">
+        <f t="shared" si="3"/>
+        <v>3.2952241812295398E-2</v>
+      </c>
+      <c r="G39">
+        <v>3</v>
+      </c>
+      <c r="J39" t="str">
+        <f t="shared" si="4"/>
+        <v>NI</v>
+      </c>
+      <c r="K39" t="str">
+        <f t="shared" si="5"/>
+        <v>e_w167300914-220</v>
+      </c>
+      <c r="L39" t="s">
+        <v>756</v>
+      </c>
+      <c r="M39" t="s">
+        <v>723</v>
+      </c>
+      <c r="N39" s="2">
+        <f t="shared" si="6"/>
+        <v>0.125235778416185</v>
+      </c>
+      <c r="O39">
+        <v>3</v>
+      </c>
+      <c r="Q39" t="str">
+        <f t="shared" si="7"/>
+        <v>NI</v>
+      </c>
+      <c r="R39" t="str">
+        <f t="shared" si="8"/>
+        <v>e_w167300914-220</v>
+      </c>
+      <c r="S39" t="s">
+        <v>755</v>
+      </c>
+      <c r="T39" t="s">
+        <v>723</v>
+      </c>
+      <c r="U39" s="2">
+        <f t="shared" si="9"/>
+        <v>4.1728863803209698E-2</v>
+      </c>
+      <c r="V39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B40" t="str">
+        <f t="shared" si="2"/>
+        <v>NI</v>
+      </c>
+      <c r="C40" t="str">
+        <f t="shared" si="2"/>
+        <v>e_w270022030-220</v>
+      </c>
+      <c r="D40" t="s">
+        <v>757</v>
+      </c>
+      <c r="E40" t="s">
+        <v>723</v>
+      </c>
+      <c r="F40" s="2">
+        <f t="shared" si="3"/>
+        <v>2.34291321054837E-2</v>
+      </c>
+      <c r="G40">
+        <v>3</v>
+      </c>
+      <c r="J40" t="str">
+        <f t="shared" si="4"/>
+        <v>NI</v>
+      </c>
+      <c r="K40" t="str">
+        <f t="shared" si="5"/>
+        <v>e_w270022030-220</v>
+      </c>
+      <c r="L40" t="s">
+        <v>756</v>
+      </c>
+      <c r="M40" t="s">
+        <v>723</v>
+      </c>
+      <c r="N40" s="2">
+        <f t="shared" si="6"/>
+        <v>9.4538907932051705E-2</v>
+      </c>
+      <c r="O40">
+        <v>3</v>
+      </c>
+      <c r="Q40" t="str">
+        <f t="shared" si="7"/>
+        <v>NI</v>
+      </c>
+      <c r="R40" t="str">
+        <f t="shared" si="8"/>
+        <v>e_w270022030-220</v>
+      </c>
+      <c r="S40" t="s">
+        <v>755</v>
+      </c>
+      <c r="T40" t="s">
+        <v>723</v>
+      </c>
+      <c r="U40" s="2">
+        <f t="shared" si="9"/>
+        <v>3.4106576172306398E-2</v>
+      </c>
+      <c r="V40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B41" t="str">
+        <f t="shared" si="2"/>
+        <v>NI</v>
+      </c>
+      <c r="C41" t="str">
+        <f t="shared" si="2"/>
+        <v>e_w907631032-220</v>
+      </c>
+      <c r="D41" t="s">
+        <v>757</v>
+      </c>
+      <c r="E41" t="s">
+        <v>723</v>
+      </c>
+      <c r="F41" s="2">
+        <f t="shared" si="3"/>
+        <v>0.63543589233768305</v>
+      </c>
+      <c r="G41">
+        <v>3</v>
+      </c>
+      <c r="J41" t="str">
+        <f t="shared" si="4"/>
+        <v>NI</v>
+      </c>
+      <c r="K41" t="str">
+        <f t="shared" si="5"/>
+        <v>e_w907631032-220</v>
+      </c>
+      <c r="L41" t="s">
+        <v>756</v>
+      </c>
+      <c r="M41" t="s">
+        <v>723</v>
+      </c>
+      <c r="N41" s="2">
+        <f t="shared" si="6"/>
+        <v>4.2286542778396897E-3</v>
+      </c>
+      <c r="O41">
+        <v>3</v>
+      </c>
+      <c r="Q41" t="str">
+        <f t="shared" si="7"/>
+        <v>NI</v>
+      </c>
+      <c r="R41" t="str">
+        <f t="shared" si="8"/>
+        <v>e_w907631032-220</v>
+      </c>
+      <c r="S41" t="s">
+        <v>755</v>
+      </c>
+      <c r="T41" t="s">
+        <v>723</v>
+      </c>
+      <c r="U41" s="2">
+        <f t="shared" si="9"/>
+        <v>0.52395618435339197</v>
+      </c>
+      <c r="V41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B42" t="str">
+        <f t="shared" si="2"/>
+        <v>NI</v>
+      </c>
+      <c r="C42" t="str">
+        <f t="shared" si="2"/>
+        <v>e_w1167708390-220</v>
+      </c>
+      <c r="D42" t="s">
+        <v>757</v>
+      </c>
+      <c r="E42" t="s">
+        <v>723</v>
+      </c>
+      <c r="F42" s="2">
+        <f t="shared" si="3"/>
+        <v>8.5661305450976596E-3</v>
+      </c>
+      <c r="G42">
+        <v>3</v>
+      </c>
+      <c r="J42" t="str">
+        <f t="shared" si="4"/>
+        <v>NI</v>
+      </c>
+      <c r="K42" t="str">
+        <f t="shared" si="5"/>
+        <v>e_w1167708390-220</v>
+      </c>
+      <c r="L42" t="s">
+        <v>756</v>
+      </c>
+      <c r="M42" t="s">
+        <v>723</v>
+      </c>
+      <c r="N42" s="2">
+        <f t="shared" si="6"/>
+        <v>9.8552632363159004E-2</v>
+      </c>
+      <c r="O42">
+        <v>3</v>
+      </c>
+      <c r="Q42" t="str">
+        <f t="shared" si="7"/>
+        <v>NI</v>
+      </c>
+      <c r="R42" t="str">
+        <f t="shared" si="8"/>
+        <v>e_w1167708390-220</v>
+      </c>
+      <c r="S42" t="s">
+        <v>755</v>
+      </c>
+      <c r="T42" t="s">
+        <v>723</v>
+      </c>
+      <c r="U42" s="2">
+        <f t="shared" si="9"/>
+        <v>2.2210244360566699E-2</v>
+      </c>
+      <c r="V42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B43" t="str">
+        <f t="shared" si="2"/>
+        <v>NI</v>
+      </c>
+      <c r="C43" t="str">
+        <f t="shared" si="2"/>
+        <v>e_w1363994055-220</v>
+      </c>
+      <c r="D43" t="s">
+        <v>757</v>
+      </c>
+      <c r="E43" t="s">
+        <v>723</v>
+      </c>
+      <c r="F43" s="2">
+        <f t="shared" si="3"/>
+        <v>8.8870686785993705E-2</v>
+      </c>
+      <c r="G43">
+        <v>3</v>
+      </c>
+      <c r="J43" t="str">
+        <f t="shared" si="4"/>
+        <v>NI</v>
+      </c>
+      <c r="K43" t="str">
+        <f t="shared" si="5"/>
+        <v>e_w1363994055-220</v>
+      </c>
+      <c r="L43" t="s">
+        <v>756</v>
+      </c>
+      <c r="M43" t="s">
+        <v>723</v>
+      </c>
+      <c r="N43" s="2">
+        <f t="shared" si="6"/>
+        <v>4.8221286775162204E-3</v>
+      </c>
+      <c r="O43">
+        <v>3</v>
+      </c>
+      <c r="Q43" t="str">
+        <f t="shared" si="7"/>
+        <v>NI</v>
+      </c>
+      <c r="R43" t="str">
+        <f t="shared" si="8"/>
+        <v>e_w1363994055-220</v>
+      </c>
+      <c r="S43" t="s">
+        <v>755</v>
+      </c>
+      <c r="T43" t="s">
+        <v>723</v>
+      </c>
+      <c r="U43" s="2">
+        <f t="shared" si="9"/>
+        <v>8.6485932091261195E-2</v>
+      </c>
+      <c r="V43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B44" t="str">
+        <f t="shared" si="2"/>
+        <v>NI</v>
+      </c>
+      <c r="C44" t="str">
+        <f t="shared" si="2"/>
+        <v>e_NZ11-220</v>
+      </c>
+      <c r="D44" t="s">
+        <v>757</v>
+      </c>
+      <c r="E44" t="s">
+        <v>723</v>
+      </c>
+      <c r="F44" s="2">
+        <f t="shared" si="3"/>
+        <v>8.0617065696143696E-3</v>
+      </c>
+      <c r="G44">
+        <v>3</v>
+      </c>
+      <c r="J44" t="str">
+        <f t="shared" si="4"/>
+        <v>NI</v>
+      </c>
+      <c r="K44" t="str">
+        <f t="shared" si="5"/>
+        <v>e_NZ11-220</v>
+      </c>
+      <c r="L44" t="s">
+        <v>756</v>
+      </c>
+      <c r="M44" t="s">
+        <v>723</v>
+      </c>
+      <c r="N44" s="2">
+        <f t="shared" si="6"/>
+        <v>8.1145533401035905E-2</v>
+      </c>
+      <c r="O44">
+        <v>3</v>
+      </c>
+      <c r="Q44" t="str">
+        <f t="shared" si="7"/>
+        <v>NI</v>
+      </c>
+      <c r="R44" t="str">
+        <f t="shared" si="8"/>
+        <v>e_NZ11-220</v>
+      </c>
+      <c r="S44" t="s">
+        <v>755</v>
+      </c>
+      <c r="T44" t="s">
+        <v>723</v>
+      </c>
+      <c r="U44" s="2">
+        <f t="shared" si="9"/>
+        <v>2.18065039073502E-2</v>
+      </c>
+      <c r="V44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B45" t="str">
+        <f t="shared" si="2"/>
+        <v>NI</v>
+      </c>
+      <c r="C45" t="str">
+        <f t="shared" si="2"/>
+        <v>e_NZ13-220</v>
+      </c>
+      <c r="D45" t="s">
+        <v>757</v>
+      </c>
+      <c r="E45" t="s">
+        <v>723</v>
+      </c>
+      <c r="F45" s="2">
+        <f t="shared" si="3"/>
+        <v>1.4923947387757999E-2</v>
+      </c>
+      <c r="G45">
+        <v>3</v>
+      </c>
+      <c r="J45" t="str">
+        <f t="shared" si="4"/>
+        <v>NI</v>
+      </c>
+      <c r="K45" t="str">
+        <f t="shared" si="5"/>
+        <v>e_NZ13-220</v>
+      </c>
+      <c r="L45" t="s">
+        <v>756</v>
+      </c>
+      <c r="M45" t="s">
+        <v>723</v>
+      </c>
+      <c r="N45" s="2">
+        <f t="shared" si="6"/>
+        <v>6.04367704312977E-2</v>
+      </c>
+      <c r="O45">
+        <v>3</v>
+      </c>
+      <c r="Q45" t="str">
+        <f t="shared" si="7"/>
+        <v>NI</v>
+      </c>
+      <c r="R45" t="str">
+        <f t="shared" si="8"/>
+        <v>e_NZ13-220</v>
+      </c>
+      <c r="S45" t="s">
+        <v>755</v>
+      </c>
+      <c r="T45" t="s">
+        <v>723</v>
+      </c>
+      <c r="U45" s="2">
+        <f t="shared" si="9"/>
+        <v>2.7299034700207302E-2</v>
+      </c>
+      <c r="V45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B46" t="str">
+        <f t="shared" si="2"/>
+        <v>SI</v>
+      </c>
+      <c r="C46" t="str">
+        <f t="shared" si="2"/>
+        <v>e_w33795353-220</v>
+      </c>
+      <c r="D46" t="s">
+        <v>757</v>
+      </c>
+      <c r="E46" t="s">
+        <v>723</v>
+      </c>
+      <c r="F46" s="2"/>
+      <c r="G46">
+        <v>3</v>
+      </c>
+      <c r="J46" t="str">
+        <f t="shared" si="4"/>
+        <v>SI</v>
+      </c>
+      <c r="K46" t="str">
+        <f t="shared" si="5"/>
+        <v>e_w33795353-220</v>
+      </c>
+      <c r="L46" t="s">
+        <v>756</v>
+      </c>
+      <c r="M46" t="s">
+        <v>723</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46">
+        <v>3</v>
+      </c>
+      <c r="Q46" t="str">
+        <f t="shared" si="7"/>
+        <v>SI</v>
+      </c>
+      <c r="R46" t="str">
+        <f t="shared" si="8"/>
+        <v>e_w33795353-220</v>
+      </c>
+      <c r="S46" t="s">
+        <v>755</v>
+      </c>
+      <c r="T46" t="s">
+        <v>723</v>
+      </c>
+      <c r="U46" s="2"/>
+      <c r="V46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B47" t="str">
+        <f t="shared" si="2"/>
+        <v>SI</v>
+      </c>
+      <c r="C47" t="str">
+        <f t="shared" si="2"/>
+        <v>e_w270521928-220</v>
+      </c>
+      <c r="D47" t="s">
+        <v>757</v>
+      </c>
+      <c r="E47" t="s">
+        <v>723</v>
+      </c>
+      <c r="F47" s="2">
+        <f t="shared" si="3"/>
+        <v>1.7574323650842699E-2</v>
+      </c>
+      <c r="G47">
+        <v>3</v>
+      </c>
+      <c r="J47" t="str">
+        <f t="shared" si="4"/>
+        <v>SI</v>
+      </c>
+      <c r="K47" t="str">
+        <f t="shared" si="5"/>
+        <v>e_w270521928-220</v>
+      </c>
+      <c r="L47" t="s">
+        <v>756</v>
+      </c>
+      <c r="M47" t="s">
+        <v>723</v>
+      </c>
+      <c r="N47" s="2">
+        <f>R17</f>
+        <v>0.142535486755099</v>
+      </c>
+      <c r="O47">
+        <v>3</v>
+      </c>
+      <c r="Q47" t="str">
+        <f t="shared" si="7"/>
+        <v>SI</v>
+      </c>
+      <c r="R47" t="str">
+        <f t="shared" si="8"/>
+        <v>e_w270521928-220</v>
+      </c>
+      <c r="S47" t="s">
+        <v>755</v>
+      </c>
+      <c r="T47" t="s">
+        <v>723</v>
+      </c>
+      <c r="U47" s="2">
+        <f t="shared" si="9"/>
+        <v>3.9025821902286997E-2</v>
+      </c>
+      <c r="V47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B48" t="str">
+        <f t="shared" si="2"/>
+        <v>SI</v>
+      </c>
+      <c r="C48" t="str">
+        <f t="shared" si="2"/>
+        <v>e_w95343089-220</v>
+      </c>
+      <c r="D48" t="s">
+        <v>757</v>
+      </c>
+      <c r="E48" t="s">
+        <v>723</v>
+      </c>
+      <c r="F48" s="2">
+        <f t="shared" si="3"/>
+        <v>0.28354990845613498</v>
+      </c>
+      <c r="G48">
+        <v>3</v>
+      </c>
+      <c r="J48" t="str">
+        <f t="shared" si="4"/>
+        <v>SI</v>
+      </c>
+      <c r="K48" t="str">
+        <f t="shared" si="5"/>
+        <v>e_w95343089-220</v>
+      </c>
+      <c r="L48" t="s">
+        <v>756</v>
+      </c>
+      <c r="M48" t="s">
+        <v>723</v>
+      </c>
+      <c r="N48" s="2">
+        <f t="shared" ref="N48:N54" si="10">R18</f>
+        <v>3.1587285738253097E-2</v>
+      </c>
+      <c r="O48">
+        <v>3</v>
+      </c>
+      <c r="Q48" t="str">
+        <f t="shared" si="7"/>
+        <v>SI</v>
+      </c>
+      <c r="R48" t="str">
+        <f t="shared" si="8"/>
+        <v>e_w95343089-220</v>
+      </c>
+      <c r="S48" t="s">
+        <v>755</v>
+      </c>
+      <c r="T48" t="s">
+        <v>723</v>
+      </c>
+      <c r="U48" s="2">
+        <f t="shared" si="9"/>
+        <v>0.244003216078024</v>
+      </c>
+      <c r="V48">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B49" t="str">
+        <f t="shared" si="2"/>
+        <v>SI</v>
+      </c>
+      <c r="C49" t="str">
+        <f t="shared" si="2"/>
+        <v>e_w100957314-220</v>
+      </c>
+      <c r="D49" t="s">
+        <v>757</v>
+      </c>
+      <c r="E49" t="s">
+        <v>723</v>
+      </c>
+      <c r="F49" s="2">
+        <f t="shared" si="3"/>
+        <v>0.50257319574648895</v>
+      </c>
+      <c r="G49">
+        <v>3</v>
+      </c>
+      <c r="J49" t="str">
+        <f t="shared" si="4"/>
+        <v>SI</v>
+      </c>
+      <c r="K49" t="str">
+        <f t="shared" si="5"/>
+        <v>e_w100957314-220</v>
+      </c>
+      <c r="L49" t="s">
+        <v>756</v>
+      </c>
+      <c r="M49" t="s">
+        <v>723</v>
+      </c>
+      <c r="N49" s="2">
+        <f t="shared" si="10"/>
+        <v>3.2834920354623598E-2</v>
+      </c>
+      <c r="O49">
+        <v>3</v>
+      </c>
+      <c r="Q49" t="str">
+        <f t="shared" si="7"/>
+        <v>SI</v>
+      </c>
+      <c r="R49" t="str">
+        <f t="shared" si="8"/>
+        <v>e_w100957314-220</v>
+      </c>
+      <c r="S49" t="s">
+        <v>755</v>
+      </c>
+      <c r="T49" t="s">
+        <v>723</v>
+      </c>
+      <c r="U49" s="2">
+        <f t="shared" si="9"/>
+        <v>0.41279623790913</v>
+      </c>
+      <c r="V49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B50" t="str">
+        <f t="shared" si="2"/>
+        <v>SI</v>
+      </c>
+      <c r="C50" t="str">
+        <f t="shared" si="2"/>
+        <v>e_w167286837-220</v>
+      </c>
+      <c r="D50" t="s">
+        <v>757</v>
+      </c>
+      <c r="E50" t="s">
+        <v>723</v>
+      </c>
+      <c r="F50" s="2">
+        <f t="shared" si="3"/>
+        <v>3.60680205016288E-2</v>
+      </c>
+      <c r="G50">
+        <v>3</v>
+      </c>
+      <c r="J50" t="str">
+        <f t="shared" si="4"/>
+        <v>SI</v>
+      </c>
+      <c r="K50" t="str">
+        <f t="shared" si="5"/>
+        <v>e_w167286837-220</v>
+      </c>
+      <c r="L50" t="s">
+        <v>756</v>
+      </c>
+      <c r="M50" t="s">
+        <v>723</v>
+      </c>
+      <c r="N50" s="2">
+        <f t="shared" si="10"/>
+        <v>0.191013906423359</v>
+      </c>
+      <c r="O50">
+        <v>3</v>
+      </c>
+      <c r="Q50" t="str">
+        <f t="shared" si="7"/>
+        <v>SI</v>
+      </c>
+      <c r="R50" t="str">
+        <f t="shared" si="8"/>
+        <v>e_w167286837-220</v>
+      </c>
+      <c r="S50" t="s">
+        <v>755</v>
+      </c>
+      <c r="T50" t="s">
+        <v>723</v>
+      </c>
+      <c r="U50" s="2">
+        <f t="shared" si="9"/>
+        <v>5.3278219512109801E-2</v>
+      </c>
+      <c r="V50">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B51" t="str">
+        <f t="shared" si="2"/>
+        <v>SI</v>
+      </c>
+      <c r="C51" t="str">
+        <f t="shared" si="2"/>
+        <v>e_w180519027-220</v>
+      </c>
+      <c r="D51" t="s">
+        <v>757</v>
+      </c>
+      <c r="E51" t="s">
+        <v>723</v>
+      </c>
+      <c r="F51" s="2">
+        <f t="shared" si="3"/>
+        <v>3.34436756042156E-2</v>
+      </c>
+      <c r="G51">
+        <v>3</v>
+      </c>
+      <c r="J51" t="str">
+        <f t="shared" si="4"/>
+        <v>SI</v>
+      </c>
+      <c r="K51" t="str">
+        <f t="shared" si="5"/>
+        <v>e_w180519027-220</v>
+      </c>
+      <c r="L51" t="s">
+        <v>756</v>
+      </c>
+      <c r="M51" t="s">
+        <v>723</v>
+      </c>
+      <c r="N51" s="2">
+        <f t="shared" si="10"/>
+        <v>4.7306892983382899E-2</v>
+      </c>
+      <c r="O51">
+        <v>3</v>
+      </c>
+      <c r="Q51" t="str">
+        <f t="shared" si="7"/>
+        <v>SI</v>
+      </c>
+      <c r="R51" t="str">
+        <f t="shared" si="8"/>
+        <v>e_w180519027-220</v>
+      </c>
+      <c r="S51" t="s">
+        <v>755</v>
+      </c>
+      <c r="T51" t="s">
+        <v>723</v>
+      </c>
+      <c r="U51" s="2">
+        <f t="shared" si="9"/>
+        <v>5.1255735460109399E-2</v>
+      </c>
+      <c r="V51">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B52" t="str">
+        <f t="shared" si="2"/>
+        <v>SI</v>
+      </c>
+      <c r="C52" t="str">
+        <f t="shared" si="2"/>
+        <v>e_w268826084-220</v>
+      </c>
+      <c r="D52" t="s">
+        <v>757</v>
+      </c>
+      <c r="E52" t="s">
+        <v>723</v>
+      </c>
+      <c r="F52" s="2">
+        <f t="shared" si="3"/>
+        <v>2.3213845419396702E-2</v>
+      </c>
+      <c r="G52">
+        <v>3</v>
+      </c>
+      <c r="J52" t="str">
+        <f t="shared" si="4"/>
+        <v>SI</v>
+      </c>
+      <c r="K52" t="str">
+        <f t="shared" si="5"/>
+        <v>e_w268826084-220</v>
+      </c>
+      <c r="L52" t="s">
+        <v>756</v>
+      </c>
+      <c r="M52" t="s">
+        <v>723</v>
+      </c>
+      <c r="N52" s="2">
+        <f t="shared" si="10"/>
+        <v>0.12562350163285799</v>
+      </c>
+      <c r="O52">
+        <v>3</v>
+      </c>
+      <c r="Q52" t="str">
+        <f t="shared" si="7"/>
+        <v>SI</v>
+      </c>
+      <c r="R52" t="str">
+        <f t="shared" si="8"/>
+        <v>e_w268826084-220</v>
+      </c>
+      <c r="S52" t="s">
+        <v>755</v>
+      </c>
+      <c r="T52" t="s">
+        <v>723</v>
+      </c>
+      <c r="U52" s="2">
+        <f t="shared" si="9"/>
+        <v>4.3371989530273498E-2</v>
+      </c>
+      <c r="V52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B53" t="str">
+        <f t="shared" si="2"/>
+        <v>SI</v>
+      </c>
+      <c r="C53" t="str">
+        <f t="shared" si="2"/>
+        <v>e_w272195826-220</v>
+      </c>
+      <c r="D53" t="s">
+        <v>757</v>
+      </c>
+      <c r="E53" t="s">
+        <v>723</v>
+      </c>
+      <c r="F53" s="2">
+        <f t="shared" si="3"/>
+        <v>6.2460982378461698E-2</v>
+      </c>
+      <c r="G53">
+        <v>3</v>
+      </c>
+      <c r="J53" t="str">
+        <f t="shared" si="4"/>
+        <v>SI</v>
+      </c>
+      <c r="K53" t="str">
+        <f t="shared" si="5"/>
+        <v>e_w272195826-220</v>
+      </c>
+      <c r="L53" t="s">
+        <v>756</v>
+      </c>
+      <c r="M53" t="s">
+        <v>723</v>
+      </c>
+      <c r="N53" s="2">
+        <f t="shared" si="10"/>
+        <v>0.16693725652546401</v>
+      </c>
+      <c r="O53">
+        <v>3</v>
+      </c>
+      <c r="Q53" t="str">
+        <f t="shared" si="7"/>
+        <v>SI</v>
+      </c>
+      <c r="R53" t="str">
+        <f t="shared" si="8"/>
+        <v>e_w272195826-220</v>
+      </c>
+      <c r="S53" t="s">
+        <v>755</v>
+      </c>
+      <c r="T53" t="s">
+        <v>723</v>
+      </c>
+      <c r="U53" s="2">
+        <f t="shared" si="9"/>
+        <v>7.3618284011086901E-2</v>
+      </c>
+      <c r="V53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B54" t="str">
+        <f t="shared" si="2"/>
+        <v>SI</v>
+      </c>
+      <c r="C54" t="str">
+        <f t="shared" si="2"/>
+        <v>e_NZ27-220</v>
+      </c>
+      <c r="D54" t="s">
+        <v>757</v>
+      </c>
+      <c r="E54" t="s">
+        <v>723</v>
+      </c>
+      <c r="F54" s="2">
+        <f t="shared" si="3"/>
+        <v>1.9672750355421001E-2</v>
+      </c>
+      <c r="G54">
+        <v>3</v>
+      </c>
+      <c r="J54" t="str">
+        <f t="shared" si="4"/>
+        <v>SI</v>
+      </c>
+      <c r="K54" t="str">
+        <f t="shared" si="5"/>
+        <v>e_NZ27-220</v>
+      </c>
+      <c r="L54" t="s">
+        <v>756</v>
+      </c>
+      <c r="M54" t="s">
+        <v>723</v>
+      </c>
+      <c r="N54" s="2">
+        <f t="shared" si="10"/>
+        <v>0.198521825937094</v>
+      </c>
+      <c r="O54">
+        <v>3</v>
+      </c>
+      <c r="Q54" t="str">
+        <f t="shared" si="7"/>
+        <v>SI</v>
+      </c>
+      <c r="R54" t="str">
+        <f t="shared" si="8"/>
+        <v>e_NZ27-220</v>
+      </c>
+      <c r="S54" t="s">
+        <v>755</v>
+      </c>
+      <c r="T54" t="s">
+        <v>723</v>
+      </c>
+      <c r="U54" s="2">
+        <f t="shared" si="9"/>
+        <v>4.0643000554560903E-2</v>
+      </c>
+      <c r="V54">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AL40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -13274,7 +15798,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{320A1887-1B0C-44A8-9658-90FD86FEE0A5}">
   <dimension ref="A9:J23"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -13515,7 +16039,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC33DFE9-8C65-4A33-8FAE-96323628CE2A}">
   <dimension ref="A1:D697"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>

--- a/SuppXLS/Scen_Base_VS.xlsx
+++ b/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B466BFD1-5E85-4066-9704-A6C54174F8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B98B8C1-09C8-438C-8BFC-A053C54AB621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="5" r:id="rId1"/>
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3900" uniqueCount="759">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3901" uniqueCount="760">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -2405,6 +2405,9 @@
   </si>
   <si>
     <t>AGRCO2,COMCO2,ELCCO2,GASCO2,INDCO2,REFCO2,RESCO2,TRACO2,co2</t>
+  </si>
+  <si>
+    <t>g_inter-island_HVDC</t>
   </si>
 </sst>
 </file>
@@ -11830,6 +11833,18 @@
       </c>
     </row>
     <row r="160" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B160" t="s">
+        <v>759</v>
+      </c>
+      <c r="C160">
+        <v>1.4</v>
+      </c>
+      <c r="D160">
+        <v>1000</v>
+      </c>
+      <c r="E160">
+        <v>0.99</v>
+      </c>
       <c r="U160" t="s">
         <v>91</v>
       </c>

--- a/SuppXLS/Scen_Base_VS.xlsx
+++ b/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B98B8C1-09C8-438C-8BFC-A053C54AB621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D691EE93-C490-483B-91FD-988D017527EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11837,10 +11837,10 @@
         <v>759</v>
       </c>
       <c r="C160">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="D160">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="E160">
         <v>0.99</v>

--- a/SuppXLS/Scen_Base_VS.xlsx
+++ b/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D691EE93-C490-483B-91FD-988D017527EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A67770-60D0-49F3-A665-C455411E69E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3901" uniqueCount="760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3901" uniqueCount="761">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -2408,6 +2408,9 @@
   </si>
   <si>
     <t>g_inter-island_HVDC</t>
+  </si>
+  <si>
+    <t>~TFM_INS-AT: curr=USD24</t>
   </si>
 </sst>
 </file>
@@ -2902,7 +2905,7 @@
   <sheetData>
     <row r="2" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
-        <v>0</v>
+        <v>760</v>
       </c>
       <c r="H2" t="s">
         <v>251</v>
